--- a/data/merged/2026-09-28/MERGED_UK_Mite-Vacuum_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_UK_Mite-Vacuum_2026-09-28.xlsx
@@ -1991,13 +1991,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2035,13 +2035,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2079,13 +2079,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2123,13 +2123,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2167,13 +2167,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2211,13 +2211,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2576,7 +2576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR15"/>
+  <dimension ref="A1:BR14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -4386,52 +4386,57 @@
       <c r="B8" s="13"/>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTVR91</t>
-        </is>
-      </c>
-      <c r="D8" s="14"/>
+          <t>B0D7HF8S2W</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Colour Name: Matte Black</t>
+        </is>
+      </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Material: Plastic | Special feature: Cordless | Brand: OSALADI | Size: 11.00X8.50X6.00CMx3pcs | Manufacturer: OSALADI | Included components: towel rack | Model name: Futon Vacuums | Item weight: 147 Grams | Unit count: 1.0 count</t>
+          <t>Brand: Minthouz | Special feature: Corded, HEPA, High Precision Sensors, UV Light | Filter type: HEPA Filter | Surface recommendation: mattress | Power source: Corded Electric</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>OSALADI</t>
+          <t>Minthouz</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>OSALADI 3pcs Vacuum Wall Support Plastic Vacuum Holder for Wall Mounted Use Cordless Accessories Supports for Home Cleaning</t>
+          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine with 2 HEPA, Heating &amp; Indicator Mite Vacuum Cleaner for Bed/Sofa/Mattress</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>Vacuum holder-- its innovative design allows you to hang the vacuum cleaner on the wall, saving space and creating a clutter- environment.
-Cordless vacuum accessories-- with its space-saving design, you can easily hang the vacuum cleaner on the wall, freeing up valuable floor space.
-Plastic vacuum holder-- made of plastic materials, it provides stable support for the vacuum cleaner and prevents it from falling.
-Wall mount for vacuum-- its durable design guarantees a long lifespan, making it a reliable and durable addition to your cleaning routine.
-Vacuum support-- its durable construction guarantees a product that can withstand daily use without getting damaged.</t>
+          <t>【Say Hi to Health!】Minthouz mattress vacuum cleaner incorporates advanced Dust Sensing Technology and a Dust Indicator that allows you to easily spot areas that need to be cleaned.The 450W motor makes the dust mite remover smaller, lighter, quieter and still delivers MAX suction. Combined with dual rollers, 60°C hot air system and 253.7nm UVC lamp integrated design, NO more mites, but ONLY a healthy and clean environment.
+【Is cleaning equipment heavy and time-consuming?】 Under the premise of maintaining strong suction power equipped with high-power lightweight motor, the weight of the whole machine is about 3.6KG, and the aerodynamic streamlined design can make the bed vacuum cleaner push process more silky smooth to a certain extent. The large chassis design allows the one-time cleaning area to be enlarged by about 𝟭.𝟱 times (Max 500c㎡), which reduces your mattress cleaning time by about 𝟯𝟬% !
+【Worried about damaging mattress?】 Minthouz mite vacuum cleaner adopts double Air Duct &amp; Roller system, which not only reduces the probability of air duct clogging by 𝟱𝟬% from the root, but also makes a cleaning to achieve 𝟮 times the effect. 𝟮×60,000rpm high vibration frequency combined with soft rubber material brush, not only protect the bed sheet, but also most of the mites and dust will be slapped down and sucked into our mattress cleaner, which is mite allergy people absolute gospel!
+*𝗪𝗮𝗿𝗺 𝘁𝗶𝗽: 𝟭. Both of our roller brushes are equipped with double locking buttons, which effectively prevents the roller from coming loose and makes it easy for you to dismantle &amp; clean them at the same time. 𝟮. Our 300ml filter adopts three layers of high-efficiency protection to ensure that it will not cause secondary pollution, so it is also a disposable accessory. The display will indicate when filter is full. (Please refer to the enclosed instruction manual for more information)
+【Still plagued by monsoon humidity?】 Studies have shown that mites will thrive in humid environments at 30℃, and will die when the temperature is above 55℃. However, our vacuum provide hot air up to 60°C, which is enough to send the mites away from the Earth. Equipped with large air vent cooling system at the tail end, it can increase the cooling efficiency by about 𝟲𝟳%! (Tip: As the vacuum is made of advanced temperature-conducting material, the surface will inevitably warm up after long use)
+【Mite Buster】 Our dust mite vacuum cleaner is also designed to incorporate a UV Lamp Sterilization feature that provides light in the 253.7nm band, which combines powerful suction, dual roller &amp; hot wind system to remove up to 𝟵𝟵.𝟵𝟵% of mites. The dust mite sensor allows you to clearly see the area you need to focus on and the gravity sensing system automatically stops the UV light when the handheld vacuum is higher than 5cm or tilted 30° to give you the most comprehensive protection!</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
         </is>
       </c>
       <c r="K8" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31W1ZXCx81L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>B0D5WTH79H</t>
+          <t>B0H8S6713Z</t>
         </is>
       </c>
       <c r="M8" s="14" t="inlineStr">
@@ -4445,7 +4450,7 @@
         </is>
       </c>
       <c r="O8" s="15">
-        <v>3802207</v>
+        <v>333633</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="16">
@@ -4458,7 +4463,7 @@
       </c>
       <c r="S8" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="T8" s="15"/>
@@ -4469,13 +4474,19 @@
       <c r="Y8" s="19">
         <v>1</v>
       </c>
-      <c r="Z8" s="20"/>
+      <c r="Z8" s="20">
+        <v>19.52</v>
+      </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="2"/>
-      <c r="AD8" s="19"/>
+      <c r="AD8" s="19">
+        <v>87</v>
+      </c>
       <c r="AE8" s="15"/>
-      <c r="AF8" s="21"/>
+      <c r="AF8" s="21">
+        <v>3.9</v>
+      </c>
       <c r="AG8" s="22">
         <v>0</v>
       </c>
@@ -4488,18 +4499,30 @@
       <c r="AL8" s="19"/>
       <c r="AM8" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN8" s="13"/>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AN8" s="13" t="inlineStr">
+        <is>
+          <t>10天</t>
+        </is>
+      </c>
       <c r="AO8" s="13"/>
-      <c r="AP8" s="20"/>
+      <c r="AP8" s="20">
+        <v>51.92</v>
+      </c>
       <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="14"/>
+      <c r="AR8" s="19">
+        <v>1</v>
+      </c>
+      <c r="AS8" s="14" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="AT8" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AU8" s="13"/>
@@ -4527,17 +4550,17 @@
       <c r="BI8" s="23"/>
       <c r="BJ8" s="23" t="inlineStr">
         <is>
-          <t>147 Grams</t>
+          <t>3.6 Kilograms</t>
         </is>
       </c>
       <c r="BK8" s="23" t="inlineStr">
         <is>
-          <t>147.00 g</t>
+          <t>3.60 kg</t>
         </is>
       </c>
       <c r="BL8" s="23" t="inlineStr">
         <is>
-          <t>11 x 8.5 x 18 centimetres</t>
+          <t>26.2L x 17.5W x 25.5H centimetres</t>
         </is>
       </c>
       <c r="BM8" s="23"/>
@@ -4554,57 +4577,48 @@
       <c r="B9" s="13"/>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>B0D7HF8S2W</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Colour Name: Matte Black</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Brand: Minthouz | Special feature: Corded, HEPA, High Precision Sensors, UV Light | Filter type: HEPA Filter | Surface recommendation: mattress | Power source: Corded Electric</t>
-        </is>
-      </c>
+          <t>B0DSCSR4MB</t>
+        </is>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Minthouz</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Minthouz Mattress Vacuum Cleaner with UV Light &amp; Dust Mite Sensor, Double Roller Handheld Futon Vacuum Bed Cleaner Machine with 2 HEPA, Heating &amp; Indicator Mite Vacuum Cleaner for Bed/Sofa/Mattress</t>
+          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; Sofa</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
-          <t>【Say Hi to Health!】Minthouz mattress vacuum cleaner incorporates advanced Dust Sensing Technology and a Dust Indicator that allows you to easily spot areas that need to be cleaned.The 450W motor makes the dust mite remover smaller, lighter, quieter and still delivers MAX suction. Combined with dual rollers, 60°C hot air system and 253.7nm UVC lamp integrated design, NO more mites, but ONLY a healthy and clean environment.
-【Is cleaning equipment heavy and time-consuming?】 Under the premise of maintaining strong suction power equipped with high-power lightweight motor, the weight of the whole machine is about 3.6KG, and the aerodynamic streamlined design can make the bed vacuum cleaner push process more silky smooth to a certain extent. The large chassis design allows the one-time cleaning area to be enlarged by about 𝟭.𝟱 times (Max 500c㎡), which reduces your mattress cleaning time by about 𝟯𝟬% !
-【Worried about damaging mattress?】 Minthouz mite vacuum cleaner adopts double Air Duct &amp; Roller system, which not only reduces the probability of air duct clogging by 𝟱𝟬% from the root, but also makes a cleaning to achieve 𝟮 times the effect. 𝟮×60,000rpm high vibration frequency combined with soft rubber material brush, not only protect the bed sheet, but also most of the mites and dust will be slapped down and sucked into our mattress cleaner, which is mite allergy people absolute gospel!
-*𝗪𝗮𝗿𝗺 𝘁𝗶𝗽: 𝟭. Both of our roller brushes are equipped with double locking buttons, which effectively prevents the roller from coming loose and makes it easy for you to dismantle &amp; clean them at the same time. 𝟮. Our 300ml filter adopts three layers of high-efficiency protection to ensure that it will not cause secondary pollution, so it is also a disposable accessory. The display will indicate when filter is full. (Please refer to the enclosed instruction manual for more information)
-【Still plagued by monsoon humidity?】 Studies have shown that mites will thrive in humid environments at 30℃, and will die when the temperature is above 55℃. However, our vacuum provide hot air up to 60°C, which is enough to send the mites away from the Earth. Equipped with large air vent cooling system at the tail end, it can increase the cooling efficiency by about 𝟲𝟳%! (Tip: As the vacuum is made of advanced temperature-conducting material, the surface will inevitably warm up after long use)
-【Mite Buster】 Our dust mite vacuum cleaner is also designed to incorporate a UV Lamp Sterilization feature that provides light in the 253.7nm band, which combines powerful suction, dual roller &amp; hot wind system to remove up to 𝟵𝟵.𝟵𝟵% of mites. The dust mite sensor allows you to clearly see the area you need to focus on and the gravity sensing system automatically stops the UV light when the handheld vacuum is higher than 5cm or tilted 30° to give you the most comprehensive protection!</t>
+          <t>15 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 15 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
+Smart Mite Detection &amp; LED Display: Mattress vacuum features a sensitive mite sensor and digital display that indicates mite levels in real time (Low/Medium/High), making cleaning results easy to monitor
+3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
+Dual Dust Cup with H12 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H12-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
+Aromatherapy &amp; Extra-Long Cord: Bed cleaner includes aroma pads and an essential oil sponge slot for a fresh scent during cleaning. 5-meter power cord covers large areas like bedrooms and living rooms with ease</t>
         </is>
       </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
         </is>
       </c>
       <c r="K9" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L9" s="14" t="inlineStr">
         <is>
-          <t>B0H8S6713Z</t>
+          <t>B0DSCSR4MB</t>
         </is>
       </c>
       <c r="M9" s="14" t="inlineStr">
@@ -4618,7 +4632,7 @@
         </is>
       </c>
       <c r="O9" s="15">
-        <v>333633</v>
+        <v>376778</v>
       </c>
       <c r="P9" s="15"/>
       <c r="Q9" s="16">
@@ -4642,18 +4656,16 @@
       <c r="Y9" s="19">
         <v>1</v>
       </c>
-      <c r="Z9" s="20">
-        <v>19.52</v>
-      </c>
+      <c r="Z9" s="20"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="2"/>
       <c r="AD9" s="19">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="AE9" s="15"/>
       <c r="AF9" s="21">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AG9" s="22">
         <v>0</v>
@@ -4663,34 +4675,28 @@
         <v>0</v>
       </c>
       <c r="AJ9"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="19"/>
+      <c r="AK9" s="13" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AL9" s="19">
+        <v>460</v>
+      </c>
       <c r="AM9" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN9" s="13" t="inlineStr">
-        <is>
-          <t>10天</t>
-        </is>
-      </c>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN9" s="13"/>
       <c r="AO9" s="13"/>
-      <c r="AP9" s="20">
-        <v>51.92</v>
-      </c>
+      <c r="AP9" s="20"/>
       <c r="AQ9" s="19"/>
-      <c r="AR9" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="AR9" s="19"/>
+      <c r="AS9" s="14"/>
       <c r="AT9" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU9" s="13"/>
@@ -4712,26 +4718,34 @@
         </is>
       </c>
       <c r="BE9" s="13"/>
-      <c r="BF9" s="13"/>
+      <c r="BF9" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG9" s="13"/>
       <c r="BH9" s="14"/>
       <c r="BI9" s="23"/>
       <c r="BJ9" s="23" t="inlineStr">
         <is>
-          <t>3.6 Kilograms</t>
+          <t>1.82 kg</t>
         </is>
       </c>
       <c r="BK9" s="23" t="inlineStr">
         <is>
-          <t>3.60 kg</t>
+          <t>1.82 kg</t>
         </is>
       </c>
       <c r="BL9" s="23" t="inlineStr">
         <is>
-          <t>26.2L x 17.5W x 25.5H centimetres</t>
-        </is>
-      </c>
-      <c r="BM9" s="23"/>
+          <t>29 x 27 x 18.6 cm</t>
+        </is>
+      </c>
+      <c r="BM9" s="23" t="inlineStr">
+        <is>
+          <t>29.00 x 27.00 x 18.60 cm</t>
+        </is>
+      </c>
       <c r="BN9" s="23"/>
       <c r="BO9" s="23"/>
       <c r="BP9" s="23"/>
@@ -4745,48 +4759,52 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Brand: Tjean | Special feature: HEPA, UV Light, Washable Filter | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Corded Electric</t>
+        </is>
+      </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Tjean</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400 W Mattress Vacuum Cleaner with 15 kPa Suction for Bed &amp; Sofa</t>
+          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, Heated Air – Anti-Allergy Bed Cleaner for Mattresses, Sofas, Carpets</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>15 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 15 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
-Smart Mite Detection &amp; LED Display: Mattress vacuum features a sensitive mite sensor and digital display that indicates mite levels in real time (Low/Medium/High), making cleaning results easy to monitor
-3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
-Dual Dust Cup with H12 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H12-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
-Aromatherapy &amp; Extra-Long Cord: Bed cleaner includes aroma pads and an essential oil sponge slot for a fresh scent during cleaning. 5-meter power cord covers large areas like bedrooms and living rooms with ease</t>
+          <t>No Clogging – Dual Dust Container Our mite vacuum features a dual-chamber dust container system that prevents dust buildup and maintains strong suction power. Effective filtration ensures hygienic cleaning.
+Mite-Free – UV-C Light &amp; Ultrasound Equipped with intelligent UV lamp and ultrasound technology, our vacuum removes up to 99.9% of mites and allergens. Automatic activation provides safe, chemical-free disinfection.
+Deep Cleaning – Tapping Function &amp; Hot Air The vibration tapping function loosens deeply embedded dust and mites, while the warm airflow reduces moisture and keeps mattresses hygienically dry — ideal for allergy sufferers.
+Clean Air – HEPA Filter &amp; Anti-Hair Brush The anti-hair brush head prevents hair tangling, while the HEPA filter reliably traps fine particles and allergens — ensuring clean air.
+Versatile – For Mattresses &amp; More Perfect for mattresses, sofas, carpets, and pet areas. Effectively removes mites, dust, and pet hair for a hygienically clean home.</t>
         </is>
       </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0DSCSR4MB</t>
+          <t>B0DSFM31F7</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
@@ -4800,11 +4818,13 @@
         </is>
       </c>
       <c r="O10" s="15">
-        <v>376778</v>
-      </c>
-      <c r="P10" s="15"/>
+        <v>778522</v>
+      </c>
+      <c r="P10" s="15">
+        <v>16609</v>
+      </c>
       <c r="Q10" s="16">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R10" s="17" t="inlineStr">
         <is>
@@ -4813,7 +4833,7 @@
       </c>
       <c r="S10" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T10" s="15"/>
@@ -4824,32 +4844,38 @@
       <c r="Y10" s="19">
         <v>1</v>
       </c>
-      <c r="Z10" s="20"/>
+      <c r="Z10" s="20">
+        <v>46.8</v>
+      </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="2"/>
       <c r="AD10" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE10" s="15"/>
+        <v>29</v>
+      </c>
+      <c r="AE10" s="15">
+        <v>0</v>
+      </c>
       <c r="AF10" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG10" s="22">
         <v>0</v>
       </c>
-      <c r="AH10" s="20"/>
+      <c r="AH10" s="20">
+        <v>3.42</v>
+      </c>
       <c r="AI10" s="16">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AJ10"/>
       <c r="AK10" s="13" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="AL10" s="19">
-        <v>460</v>
+        <v>530</v>
       </c>
       <c r="AM10" s="13" t="inlineStr">
         <is>
@@ -4859,17 +4885,37 @@
       <c r="AN10" s="13"/>
       <c r="AO10" s="13"/>
       <c r="AP10" s="20"/>
-      <c r="AQ10" s="19"/>
-      <c r="AR10" s="19"/>
-      <c r="AS10" s="14"/>
+      <c r="AQ10" s="19">
+        <v>10</v>
+      </c>
+      <c r="AR10" s="19">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="14" t="inlineStr">
+        <is>
+          <t>TJean Store</t>
+        </is>
+      </c>
       <c r="AT10" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU10" s="13"/>
-      <c r="AV10" s="14"/>
-      <c r="AW10" s="13"/>
+      <c r="AU10" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV10" s="14" t="inlineStr">
+        <is>
+          <t>杭州市 余杭区 浙江省 311100 CN</t>
+        </is>
+      </c>
+      <c r="AW10" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
+        </is>
+      </c>
       <c r="AX10" s="13"/>
       <c r="AY10" s="13"/>
       <c r="AZ10" s="13"/>
@@ -4896,29 +4942,45 @@
       <c r="BI10" s="23"/>
       <c r="BJ10" s="23" t="inlineStr">
         <is>
-          <t>1.82 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BK10" s="23" t="inlineStr">
         <is>
-          <t>1.82 kg</t>
+          <t>2.22 kg</t>
         </is>
       </c>
       <c r="BL10" s="23" t="inlineStr">
         <is>
-          <t>29 x 27 x 18.6 cm</t>
-        </is>
-      </c>
-      <c r="BM10" s="23" t="inlineStr">
-        <is>
-          <t>29.00 x 27.00 x 18.60 cm</t>
-        </is>
-      </c>
-      <c r="BN10" s="23"/>
-      <c r="BO10" s="23"/>
-      <c r="BP10" s="23"/>
-      <c r="BQ10" s="23"/>
-      <c r="BR10" s="13"/>
+          <t>24L x 19.5W x 28.5H centimetres</t>
+        </is>
+      </c>
+      <c r="BM10" s="23"/>
+      <c r="BN10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BO10" s="23" t="inlineStr">
+        <is>
+          <t>2.22 kg</t>
+        </is>
+      </c>
+      <c r="BP10" s="23" t="inlineStr">
+        <is>
+          <t>32.6 x 27.5 x 21.1 cm</t>
+        </is>
+      </c>
+      <c r="BQ10" s="23" t="inlineStr">
+        <is>
+          <t>32.60 x 27.50 x 21.10 cm</t>
+        </is>
+      </c>
+      <c r="BR10" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
@@ -4927,52 +4989,48 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0DTS8VCFB</t>
         </is>
       </c>
       <c r="D11" s="14"/>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>Brand: Tjean | Special feature: HEPA, UV Light, Washable Filter | Filter type: HEPA Filter | Surface recommendation: Carpet | Power source: Corded Electric</t>
-        </is>
-      </c>
+      <c r="E11" s="14"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Tjean</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Tjean UV Mattress Vacuum Cleaner,Futon Vacuum Dust Mite Vacuum – Dual Dust Bin, UV-C&amp;Ultrasonic Mite Removal, HEPA Filter, Heated Air – Anti-Allergy Bed Cleaner for Mattresses, Sofas, Carpets</t>
+          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; Sofa</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
         <is>
-          <t>No Clogging – Dual Dust Container Our mite vacuum features a dual-chamber dust container system that prevents dust buildup and maintains strong suction power. Effective filtration ensures hygienic cleaning.
-Mite-Free – UV-C Light &amp; Ultrasound Equipped with intelligent UV lamp and ultrasound technology, our vacuum removes up to 99.9% of mites and allergens. Automatic activation provides safe, chemical-free disinfection.
-Deep Cleaning – Tapping Function &amp; Hot Air The vibration tapping function loosens deeply embedded dust and mites, while the warm airflow reduces moisture and keeps mattresses hygienically dry — ideal for allergy sufferers.
-Clean Air – HEPA Filter &amp; Anti-Hair Brush The anti-hair brush head prevents hair tangling, while the HEPA filter reliably traps fine particles and allergens — ensuring clean air.
-Versatile – For Mattresses &amp; More Perfect for mattresses, sofas, carpets, and pet areas. Effectively removes mites, dust, and pet hair for a hygienically clean home.</t>
+          <t>16 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 16 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
+3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
+Powerful Ultrasonic Deep Cleaning: Equipped with advanced ultrasonic technology, the mattress vacuum penetrates deep into fibers to break down stubborn dirt, stains, and bacteria—ensuring a thorough, damage-free clean across the entire surface
+Dual Dust Cup with H11 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H11-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
+Extra-Long Cord: The 5-meter extra-long power cord provides extended reach, allowing you to clean large spaces such as bedrooms, living rooms, and hallways without constantly switching outlets. This added convenience ensures uninterrupted cleaning and better efficiency</t>
         </is>
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B0DSFM31F7</t>
+          <t>B0DTS8VCFB</t>
         </is>
       </c>
       <c r="M11" s="14" t="inlineStr">
@@ -4986,13 +5044,11 @@
         </is>
       </c>
       <c r="O11" s="15">
-        <v>778522</v>
-      </c>
-      <c r="P11" s="15">
-        <v>16609</v>
-      </c>
+        <v>125961</v>
+      </c>
+      <c r="P11" s="15"/>
       <c r="Q11" s="16">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R11" s="17" t="inlineStr">
         <is>
@@ -5001,7 +5057,7 @@
       </c>
       <c r="S11" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T11" s="15"/>
@@ -5012,38 +5068,32 @@
       <c r="Y11" s="19">
         <v>1</v>
       </c>
-      <c r="Z11" s="20">
-        <v>46.8</v>
-      </c>
+      <c r="Z11" s="20"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="2"/>
       <c r="AD11" s="19">
-        <v>29</v>
-      </c>
-      <c r="AE11" s="15">
-        <v>0</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="AE11" s="15"/>
       <c r="AF11" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG11" s="22">
         <v>0</v>
       </c>
-      <c r="AH11" s="20">
-        <v>3.42</v>
-      </c>
+      <c r="AH11" s="20"/>
       <c r="AI11" s="16">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="AJ11"/>
       <c r="AK11" s="13" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AL11" s="19">
-        <v>530</v>
+        <v>436</v>
       </c>
       <c r="AM11" s="13" t="inlineStr">
         <is>
@@ -5053,37 +5103,17 @@
       <c r="AN11" s="13"/>
       <c r="AO11" s="13"/>
       <c r="AP11" s="20"/>
-      <c r="AQ11" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR11" s="19">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="14" t="inlineStr">
-        <is>
-          <t>TJean Store</t>
-        </is>
-      </c>
+      <c r="AQ11" s="19"/>
+      <c r="AR11" s="19"/>
+      <c r="AS11" s="14"/>
       <c r="AT11" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU11" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV11" s="14" t="inlineStr">
-        <is>
-          <t>杭州市 余杭区 浙江省 311100 CN</t>
-        </is>
-      </c>
-      <c r="AW11" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP</t>
-        </is>
-      </c>
+      <c r="AU11" s="13"/>
+      <c r="AV11" s="14"/>
+      <c r="AW11" s="13"/>
       <c r="AX11" s="13"/>
       <c r="AY11" s="13"/>
       <c r="AZ11" s="13"/>
@@ -5110,45 +5140,29 @@
       <c r="BI11" s="23"/>
       <c r="BJ11" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.56 kg</t>
         </is>
       </c>
       <c r="BK11" s="23" t="inlineStr">
         <is>
-          <t>2.22 kg</t>
+          <t>2.56 kg</t>
         </is>
       </c>
       <c r="BL11" s="23" t="inlineStr">
         <is>
-          <t>24L x 19.5W x 28.5H centimetres</t>
-        </is>
-      </c>
-      <c r="BM11" s="23"/>
-      <c r="BN11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BO11" s="23" t="inlineStr">
-        <is>
-          <t>2.22 kg</t>
-        </is>
-      </c>
-      <c r="BP11" s="23" t="inlineStr">
-        <is>
-          <t>32.6 x 27.5 x 21.1 cm</t>
-        </is>
-      </c>
-      <c r="BQ11" s="23" t="inlineStr">
-        <is>
-          <t>32.60 x 27.50 x 21.10 cm</t>
-        </is>
-      </c>
-      <c r="BR11" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>25 x 21.5 x 32.5 cm</t>
+        </is>
+      </c>
+      <c r="BM11" s="23" t="inlineStr">
+        <is>
+          <t>25.00 x 21.50 x 32.50 cm</t>
+        </is>
+      </c>
+      <c r="BN11" s="23"/>
+      <c r="BO11" s="23"/>
+      <c r="BP11" s="23"/>
+      <c r="BQ11" s="23"/>
+      <c r="BR11" s="13"/>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
@@ -5157,48 +5171,53 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0F1XRXLVK</t>
         </is>
       </c>
       <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Brand: Gxzsk | Special feature: 16KPA Strong Suction, Dual Cup &amp; Washable Filter, High Heating, UV Light &amp; Ultrasonic, Widen Suction Port &amp; Green Light Dust Display | Filter type: HEPA Filter | Surface recommendation: Mattress/Carpet/Fabric | Power source: Corded Electric</t>
+        </is>
+      </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Gxzsk</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF 400W Mattress Vacuum Cleaner with 16 kPa Suction for Bed &amp; Sofa</t>
+          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen Suction Port Handheld Vacuums for Bed, Sofa, Couch, Crib (500W, Corded)</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>16 kPa Powerful Suction: The handheld dust mite vacuum delivers strong 16 kPa suction, effectively removing mites, dust, and pet hair from fabric surfaces such as beds, mattresses, sofas, cribs, and carpets—helping keep your home clean and comfortable
-3-in-1 Mite Removal Technology: Mattress cleaner machine combines 275 nm UV-C light, 60 °C hot air, and a beating roller brush to deeply penetrate fabrics and effectively eliminate mites and bacteria
-Powerful Ultrasonic Deep Cleaning: Equipped with advanced ultrasonic technology, the mattress vacuum penetrates deep into fibers to break down stubborn dirt, stains, and bacteria—ensuring a thorough, damage-free clean across the entire surface
-Dual Dust Cup with H11 HEPA Filter: This dust mite vacuum features a 500 ml large-capacity dual dust cup and a separated filtration design to effectively prevent clogging and leakage. Equipped with an H11-grade HEPA filter, it captures fine dust particles to maintain consistent suction and enhance cleaning efficiency
-Extra-Long Cord: The 5-meter extra-long power cord provides extended reach, allowing you to clean large spaces such as bedrooms, living rooms, and hallways without constantly switching outlets. This added convenience ensures uninterrupted cleaning and better efficiency</t>
+          <t>🌀【16KPA POWERFUL SUCTION】This mattress vacuum cleaner is equipped with a 500W high-power motor that provides a powerful suction of 16kPa and high-speed vibration of 30000RPM. It can deeply penetrate through fabrics such as mattresses and sofas, shake the dust and debris inside the mattress to the surface, easily absorb hidden particles, allowing you to bid farewell to troubles such as sneezing completely. The strong suction can also easily absorb pet hair, keep the mattress clean, and create a comfortable living environment for you
+🛡️【UV-C LIGHT &amp; ULTRASONIC TECHNOLOGY】This multi-functional bed vacuum cleaner adopts a dual-effect purification technology of 253.7nm uv-c light and 40,000Hz ultrasonic waves. It penetrates deep into the mattress fibers, precisely capturing and removing 99.99% of invisible particles. This mattress cleaner also equipped with an intelligent safety system, its dual-wheel gravity sensor monitors contact surface in real time, uv-c light automatically activates only when placed horizontally and immediately deactivates when tilted or lifted, ensuring complete operational safety
+☀️【140℉ HOT AIR】This mattress vacuum cleaner is equipped with a powerful motor that continuously emits 140°F hot air, which penetrates the mattress fiber layers, destroy the living environment of harmful substances. The high-temperature hot air can also quickly evaporate the remaining moisture, keeping the mattress fresh and dry at all times, and creating a healthy and comfortable sleeping environment for you
+💡【WIDEN SUCTION PORT &amp; GREEN LIGHT DISPLAY】This mattress vacuum cleaner is equipped with an 8.7-inch widened suction port and a large-diameter anti-tangle roller brush. Combined with high-frequency beating technology, it can quickly separate embedded particles and complete the cleaning of the full-size bed in just 3 minutes. The extra-long 16.4FT power cord allows for free movement throughout the house. Paired with the intelligent green light dust display system, it can intuitively show the dust distribution in the cleaning area, saying goodbye to blind cleaning. This bed vacuum cleaner is truly a great helper for household cleaning
+💦【DUAL-CUP FILTERATION DESIGN】This handheld mattress cleaner features a dual-cup storage system, combining dual cyclone filtration and high-efficiency particulate filtration for enhanced performance. The 0.2L dust-separating cup captures hair and fibers, while the 0.4L dust-collecting cup stores debris, effectively preventing tangling. Equipped with a HEPA filter, it traps 99.99% of particles as small as 0.3 microns, preventing mattress vacuum cleaner from clogging, and extending service life. Both cups and filters are easily detachable and come with a cleaning brush for maintenance. After drying, they can be reused
+📢【NOTICE】This handheld mattress vacuum features automatic overheat protection. The roller brush is also equipped with anti-tangling protection, it will automatically stop when it gets tangled. Please clean the roller brush and filter promptly after use to prevent clogging and motor overheating. If the machine stops working, simply turn off the power and allow it to cool before resuming operation. Should you encounter any dissatisfaction while using this mattress vacuum cleaner, please don't hesitate to contact us, we're always happy to assist</t>
         </is>
       </c>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B0DTS8VCFB</t>
+          <t>B0FFZWJTL1</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
@@ -5212,7 +5231,7 @@
         </is>
       </c>
       <c r="O12" s="15">
-        <v>125961</v>
+        <v>3528062</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="16">
@@ -5225,7 +5244,7 @@
       </c>
       <c r="S12" s="18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T12" s="15"/>
@@ -5241,7 +5260,7 @@
       <c r="AB12" s="1"/>
       <c r="AC12" s="2"/>
       <c r="AD12" s="19">
-        <v>31</v>
+        <v>384</v>
       </c>
       <c r="AE12" s="15"/>
       <c r="AF12" s="21">
@@ -5255,14 +5274,8 @@
         <v>0</v>
       </c>
       <c r="AJ12"/>
-      <c r="AK12" s="13" t="inlineStr">
-        <is>
-          <t>2025-07-19</t>
-        </is>
-      </c>
-      <c r="AL12" s="19">
-        <v>436</v>
-      </c>
+      <c r="AK12" s="13"/>
+      <c r="AL12" s="19"/>
       <c r="AM12" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -5287,45 +5300,21 @@
       <c r="AZ12" s="13"/>
       <c r="BA12" s="13"/>
       <c r="BB12" s="13"/>
-      <c r="BC12" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD12" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC12" s="13"/>
+      <c r="BD12" s="13"/>
       <c r="BE12" s="13"/>
-      <c r="BF12" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF12" s="13"/>
       <c r="BG12" s="13"/>
       <c r="BH12" s="14"/>
       <c r="BI12" s="23"/>
-      <c r="BJ12" s="23" t="inlineStr">
-        <is>
-          <t>2.56 kg</t>
-        </is>
-      </c>
-      <c r="BK12" s="23" t="inlineStr">
-        <is>
-          <t>2.56 kg</t>
-        </is>
-      </c>
+      <c r="BJ12" s="23"/>
+      <c r="BK12" s="23"/>
       <c r="BL12" s="23" t="inlineStr">
         <is>
-          <t>25 x 21.5 x 32.5 cm</t>
-        </is>
-      </c>
-      <c r="BM12" s="23" t="inlineStr">
-        <is>
-          <t>25.00 x 21.50 x 32.50 cm</t>
-        </is>
-      </c>
+          <t>25.1L x 29W x 14.7H centimetres</t>
+        </is>
+      </c>
+      <c r="BM12" s="23"/>
       <c r="BN12" s="23"/>
       <c r="BO12" s="23"/>
       <c r="BP12" s="23"/>
@@ -5339,53 +5328,52 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B0F1XRXLVK</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Brand: Gxzsk | Special feature: 16KPA Strong Suction, Dual Cup &amp; Washable Filter, High Heating, UV Light &amp; Ultrasonic, Widen Suction Port &amp; Green Light Dust Display | Filter type: HEPA Filter | Surface recommendation: Mattress/Carpet/Fabric | Power source: Corded Electric</t>
+          <t>Brand: KÄRCHER | Special feature: UV-C light technology and mattress cleaning | Filter type: Foam | Surface recommendation: Upholstery | Power source: Corded Electric</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk</t>
+          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Gxzsk Mattress Vacuum Cleaner, 16kPa Bed Vacuum Cleaner with 253.7nm UV-C Light, Ultrasonic &amp; 140℉ Heating, Dual Cup &amp; Widen Suction Port Handheld Vacuums for Bed, Sofa, Couch, Crib (500W, Corded)</t>
+          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500 watts, weight: 2.1 kg, removes mites and bacteria, for people with a</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>🌀【16KPA POWERFUL SUCTION】This mattress vacuum cleaner is equipped with a 500W high-power motor that provides a powerful suction of 16kPa and high-speed vibration of 30000RPM. It can deeply penetrate through fabrics such as mattresses and sofas, shake the dust and debris inside the mattress to the surface, easily absorb hidden particles, allowing you to bid farewell to troubles such as sneezing completely. The strong suction can also easily absorb pet hair, keep the mattress clean, and create a comfortable living environment for you
-🛡️【UV-C LIGHT &amp; ULTRASONIC TECHNOLOGY】This multi-functional bed vacuum cleaner adopts a dual-effect purification technology of 253.7nm uv-c light and 40,000Hz ultrasonic waves. It penetrates deep into the mattress fibers, precisely capturing and removing 99.99% of invisible particles. This mattress cleaner also equipped with an intelligent safety system, its dual-wheel gravity sensor monitors contact surface in real time, uv-c light automatically activates only when placed horizontally and immediately deactivates when tilted or lifted, ensuring complete operational safety
-☀️【140℉ HOT AIR】This mattress vacuum cleaner is equipped with a powerful motor that continuously emits 140°F hot air, which penetrates the mattress fiber layers, destroy the living environment of harmful substances. The high-temperature hot air can also quickly evaporate the remaining moisture, keeping the mattress fresh and dry at all times, and creating a healthy and comfortable sleeping environment for you
-💡【WIDEN SUCTION PORT &amp; GREEN LIGHT DISPLAY】This mattress vacuum cleaner is equipped with an 8.7-inch widened suction port and a large-diameter anti-tangle roller brush. Combined with high-frequency beating technology, it can quickly separate embedded particles and complete the cleaning of the full-size bed in just 3 minutes. The extra-long 16.4FT power cord allows for free movement throughout the house. Paired with the intelligent green light dust display system, it can intuitively show the dust distribution in the cleaning area, saying goodbye to blind cleaning. This bed vacuum cleaner is truly a great helper for household cleaning
-💦【DUAL-CUP FILTERATION DESIGN】This handheld mattress cleaner features a dual-cup storage system, combining dual cyclone filtration and high-efficiency particulate filtration for enhanced performance. The 0.2L dust-separating cup captures hair and fibers, while the 0.4L dust-collecting cup stores debris, effectively preventing tangling. Equipped with a HEPA filter, it traps 99.99% of particles as small as 0.3 microns, preventing mattress vacuum cleaner from clogging, and extending service life. Both cups and filters are easily detachable and come with a cleaning brush for maintenance. After drying, they can be reused
-📢【NOTICE】This handheld mattress vacuum features automatic overheat protection. The roller brush is also equipped with anti-tangling protection, it will automatically stop when it gets tangled. Please clean the roller brush and filter promptly after use to prevent clogging and motor overheating. If the machine stops working, simply turn off the power and allow it to cool before resuming operation. Should you encounter any dissatisfaction while using this mattress vacuum cleaner, please don't hesitate to contact us, we're always happy to assist</t>
+          <t>Hygienic deep cleaning: the VCH 4 UVClean cleans mattresses, pillows, other textile surfaces and frees them from visible and invisible contamination
+3-way technology: the vibrating knock roller dissolves deep seated dirt and mites, which are then thoroughly vacuumed; the UV-C light neutralises 99.9% of all bacteria and mites
+Container system with 2 compartments: cyclone technology ensures that coarse dirt is collected in one and fine dust in the other chamber; this ensures consistently high suction power
+Compact design: the device with the ergonomic handle weighs 2.1 kg and allows for a long and effortless work; after cleaning, it can be stored away to save space
+Contents: Kärcher mattress cleaner VCH 4 UVClean, knock roller, 2 foam filters, 3 engine protection filters</t>
         </is>
       </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B0FFZWJTL1</t>
+          <t>B0FPQMRBYZ</t>
         </is>
       </c>
       <c r="M13" s="14" t="inlineStr">
@@ -5399,11 +5387,13 @@
         </is>
       </c>
       <c r="O13" s="15">
-        <v>3528062</v>
-      </c>
-      <c r="P13" s="15"/>
+        <v>339242</v>
+      </c>
+      <c r="P13" s="15">
+        <v>-27530</v>
+      </c>
       <c r="Q13" s="16">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R13" s="17" t="inlineStr">
         <is>
@@ -5412,38 +5402,52 @@
       </c>
       <c r="S13" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T13" s="15"/>
-      <c r="U13" s="16"/>
+      <c r="U13" s="16">
+        <v>-1</v>
+      </c>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
       <c r="Y13" s="19">
         <v>1</v>
       </c>
-      <c r="Z13" s="20"/>
+      <c r="Z13" s="20">
+        <v>142.98</v>
+      </c>
       <c r="AA13" s="4"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="2"/>
       <c r="AD13" s="19">
-        <v>384</v>
-      </c>
-      <c r="AE13" s="15"/>
+        <v>196</v>
+      </c>
+      <c r="AE13" s="15">
+        <v>19</v>
+      </c>
       <c r="AF13" s="21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
       </c>
-      <c r="AH13" s="20"/>
+      <c r="AH13" s="20">
+        <v>3.43</v>
+      </c>
       <c r="AI13" s="16">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AJ13"/>
-      <c r="AK13" s="13"/>
-      <c r="AL13" s="19"/>
+      <c r="AK13" s="13" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="AL13" s="19">
+        <v>298</v>
+      </c>
       <c r="AM13" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -5452,17 +5456,37 @@
       <c r="AN13" s="13"/>
       <c r="AO13" s="13"/>
       <c r="AP13" s="20"/>
-      <c r="AQ13" s="19"/>
-      <c r="AR13" s="19"/>
-      <c r="AS13" s="14"/>
+      <c r="AQ13" s="19">
+        <v>9</v>
+      </c>
+      <c r="AR13" s="19">
+        <v>2</v>
+      </c>
+      <c r="AS13" s="14" t="inlineStr">
+        <is>
+          <t>Daily Discounts Ltd</t>
+        </is>
+      </c>
       <c r="AT13" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU13" s="13"/>
-      <c r="AV13" s="14"/>
-      <c r="AW13" s="13"/>
+      <c r="AU13" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV13" s="14" t="inlineStr">
+        <is>
+          <t>London Greater London E6 5YU GB</t>
+        </is>
+      </c>
+      <c r="AW13" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB</t>
+        </is>
+      </c>
       <c r="AX13" s="13"/>
       <c r="AY13" s="13"/>
       <c r="AZ13" s="13"/>
@@ -5475,19 +5499,47 @@
       <c r="BG13" s="13"/>
       <c r="BH13" s="14"/>
       <c r="BI13" s="23"/>
-      <c r="BJ13" s="23"/>
-      <c r="BK13" s="23"/>
+      <c r="BJ13" s="23" t="inlineStr">
+        <is>
+          <t>2.5 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK13" s="23" t="inlineStr">
+        <is>
+          <t>2.50 kg</t>
+        </is>
+      </c>
       <c r="BL13" s="23" t="inlineStr">
         <is>
-          <t>25.1L x 29W x 14.7H centimetres</t>
+          <t>30.9L x 24W x 17H centimetres</t>
         </is>
       </c>
       <c r="BM13" s="23"/>
-      <c r="BN13" s="23"/>
-      <c r="BO13" s="23"/>
-      <c r="BP13" s="23"/>
-      <c r="BQ13" s="23"/>
-      <c r="BR13" s="13"/>
+      <c r="BN13" s="23" t="inlineStr">
+        <is>
+          <t>3.2 kg</t>
+        </is>
+      </c>
+      <c r="BO13" s="23" t="inlineStr">
+        <is>
+          <t>3.20 kg</t>
+        </is>
+      </c>
+      <c r="BP13" s="23" t="inlineStr">
+        <is>
+          <t>39.1 x 29.4 x 19.3 cm</t>
+        </is>
+      </c>
+      <c r="BQ13" s="23" t="inlineStr">
+        <is>
+          <t>39.10 x 29.40 x 19.30 cm</t>
+        </is>
+      </c>
+      <c r="BR13" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
@@ -5496,52 +5548,56 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
-        </is>
-      </c>
-      <c r="D14" s="14"/>
+          <t>B0GJDH8XTW</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>Colour Name: Starry Gray</t>
+        </is>
+      </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Brand: KÄRCHER | Special feature: UV-C light technology and mattress cleaning | Filter type: Foam | Surface recommendation: Upholstery | Power source: Corded Electric</t>
+          <t>Brand: RANVOO | Special feature: UV Light, HEPA, High Precision Sensors, Ultrasonic Technology, Rapid Heating | Filter type: HEPA Filter | Surface recommendation: TOP 1 in New Releases | Power source: Corded Electric</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>RANVOO</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Kärcher Mattress cleaner VCH 4 UVClean, hygienic deep cleaning with UV-C light, knock roller and suction function, power 500 watts, weight: 2.1 kg, removes mites and bacteria, for people with a</t>
+          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights, Ultrasonic, HEPA Filter &amp; Sensor, for Bed, Sofa,Carpet, Corded Starry Gray</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>Hygienic deep cleaning: the VCH 4 UVClean cleans mattresses, pillows, other textile surfaces and frees them from visible and invisible contamination
-3-way technology: the vibrating knock roller dissolves deep seated dirt and mites, which are then thoroughly vacuumed; the UV-C light neutralises 99.9% of all bacteria and mites
-Container system with 2 compartments: cyclone technology ensures that coarse dirt is collected in one and fine dust in the other chamber; this ensures consistently high suction power
-Compact design: the device with the ergonomic handle weighs 2.1 kg and allows for a long and effortless work; after cleaning, it can be stored away to save space
-Contents: Kärcher mattress cleaner VCH 4 UVClean, knock roller, 2 foam filters, 3 engine protection filters</t>
+          <t>[Strongest 35kPA Dual Suction Clears 100% Allergens in One Go] Equipped with the latest 35Kpa dual suction mite and allergens removal system developed in 2024, it offers an astonishing 261% increase in suction power and a 300% larger suction area compared to the previous version. It effortlessly removes 100% of mites and allergens in one pass, solving problems like itching during sleep or nasal congestion. Give family the gift of a clean and comfortable night’s sleep.
+[Sextuple Tech in One to Achieve 100% Mites Inhibition] This bed vacuum cleaner uv sanitizing also equipped with a double-beating system of 12.8K beats per min, which will beat any bad substances in the mattress or sofa, such as dust and mites, to the surface through high-frequency beating, and then quickly suck them away. Medical-grade UV-C, ultrasonic waves and 65℃ heating system specifically designed for mites can completely kill mite eggs.
+[Pro-grade Air Purification With 6-Stage HEPA Filter and Negative Ions] RANVOO mattress vacuum is equipped with HEPA filter to achieve efficient filtration of millimeter-level particles, completely filtering out all inhaled dust, mites and allergens. RANVOO's exclusive negative oxygen ion air filtration system, which can promptly purify any dust and mites emitted from the mattress or sofa into the air when using a vacuum cleaner.
+[Easy to Use Even for Vacuum Beginners] RANVOO mattress cleaner does not require installation or any adjustments. You can start using it right after unpacking. The 400 ml large dust cup is enough to hold the dust generated by several full-house fabric cleanings, so there is no need to replace it frequently. Cleaning the dust cup and reinstalling it can also be done in tens of seconds. You can use it quickly and clean the whole house thoroughly without any tedious operations.
+[AI Chip Makes It the Best for All Fabrics] RANVOO bed vacuum is equipped with the most advanced AI chip, which can intelligently identify and adapt to any household fabrics such as mattresses, sofas, carpets and pillows, and automatically match the most suitable suction and amplitude to achieve the effect of completely removing mites and protecting the fabric itself on fabrics of different materials and depths.</t>
         </is>
       </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B0FPQMRBYZ</t>
+          <t>B0FX2VM7HM</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
@@ -5555,13 +5611,11 @@
         </is>
       </c>
       <c r="O14" s="15">
-        <v>339242</v>
-      </c>
-      <c r="P14" s="15">
-        <v>-27530</v>
-      </c>
+        <v>313519</v>
+      </c>
+      <c r="P14" s="15"/>
       <c r="Q14" s="16">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R14" s="17" t="inlineStr">
         <is>
@@ -5574,48 +5628,34 @@
         </is>
       </c>
       <c r="T14" s="15"/>
-      <c r="U14" s="16">
-        <v>-1</v>
-      </c>
+      <c r="U14" s="16"/>
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14" s="19">
         <v>1</v>
       </c>
-      <c r="Z14" s="20">
-        <v>142.98</v>
-      </c>
+      <c r="Z14" s="20"/>
       <c r="AA14" s="4"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="2"/>
       <c r="AD14" s="19">
-        <v>196</v>
-      </c>
-      <c r="AE14" s="15">
-        <v>19</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="AE14" s="15"/>
       <c r="AF14" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG14" s="22">
         <v>0</v>
       </c>
-      <c r="AH14" s="20">
-        <v>3.43</v>
-      </c>
+      <c r="AH14" s="20"/>
       <c r="AI14" s="16">
-        <v>0.98</v>
+        <v>0</v>
       </c>
       <c r="AJ14"/>
-      <c r="AK14" s="13" t="inlineStr">
-        <is>
-          <t>2025-12-03</t>
-        </is>
-      </c>
-      <c r="AL14" s="19">
-        <v>298</v>
-      </c>
+      <c r="AK14" s="13"/>
+      <c r="AL14" s="19"/>
       <c r="AM14" s="13" t="inlineStr">
         <is>
           <t>NA</t>
@@ -5624,258 +5664,50 @@
       <c r="AN14" s="13"/>
       <c r="AO14" s="13"/>
       <c r="AP14" s="20"/>
-      <c r="AQ14" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR14" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS14" s="14" t="inlineStr">
-        <is>
-          <t>Daily Discounts Ltd</t>
-        </is>
-      </c>
+      <c r="AQ14" s="19"/>
+      <c r="AR14" s="19"/>
+      <c r="AS14" s="14"/>
       <c r="AT14" s="13" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU14" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV14" s="14" t="inlineStr">
-        <is>
-          <t>London Greater London E6 5YU GB</t>
-        </is>
-      </c>
-      <c r="AW14" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB</t>
-        </is>
-      </c>
+      <c r="AU14" s="13"/>
+      <c r="AV14" s="14"/>
+      <c r="AW14" s="13"/>
       <c r="AX14" s="13"/>
       <c r="AY14" s="13"/>
       <c r="AZ14" s="13"/>
       <c r="BA14" s="13"/>
       <c r="BB14" s="13"/>
-      <c r="BC14" s="13"/>
+      <c r="BC14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD14" s="13"/>
       <c r="BE14" s="13"/>
-      <c r="BF14" s="13"/>
+      <c r="BF14" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG14" s="13"/>
       <c r="BH14" s="14"/>
       <c r="BI14" s="23"/>
-      <c r="BJ14" s="23" t="inlineStr">
-        <is>
-          <t>2.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK14" s="23" t="inlineStr">
-        <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
+      <c r="BJ14" s="23"/>
+      <c r="BK14" s="23"/>
       <c r="BL14" s="23" t="inlineStr">
         <is>
-          <t>30.9L x 24W x 17H centimetres</t>
+          <t>28.9L x 33.8W x 18.8H centimetres</t>
         </is>
       </c>
       <c r="BM14" s="23"/>
-      <c r="BN14" s="23" t="inlineStr">
-        <is>
-          <t>3.2 kg</t>
-        </is>
-      </c>
-      <c r="BO14" s="23" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
-      <c r="BP14" s="23" t="inlineStr">
-        <is>
-          <t>39.1 x 29.4 x 19.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ14" s="23" t="inlineStr">
-        <is>
-          <t>39.10 x 29.40 x 19.30 cm</t>
-        </is>
-      </c>
-      <c r="BR14" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
-        <v>14</v>
-      </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>B0GJDH8XTW</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Colour Name: Starry Gray</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>Brand: RANVOO | Special feature: UV Light, HEPA, High Precision Sensors, Ultrasonic Technology, Rapid Heating | Filter type: HEPA Filter | Surface recommendation: TOP 1 in New Releases | Power source: Corded Electric</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
-        <is>
-          <t>RANVOO</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>PureMatt Pro 35Kpa Max Suction AI Mattress Vacuum [100% Allergen, Dust &amp; Pet Hair Removal] Bed Vacuum Cleaner with UV Lights, Ultrasonic, HEPA Filter &amp; Sensor, for Bed, Sofa,Carpet, Corded Starry Gray</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>[Strongest 35kPA Dual Suction Clears 100% Allergens in One Go] Equipped with the latest 35Kpa dual suction mite and allergens removal system developed in 2024, it offers an astonishing 261% increase in suction power and a 300% larger suction area compared to the previous version. It effortlessly removes 100% of mites and allergens in one pass, solving problems like itching during sleep or nasal congestion. Give family the gift of a clean and comfortable night’s sleep.
-[Sextuple Tech in One to Achieve 100% Mites Inhibition] This bed vacuum cleaner uv sanitizing also equipped with a double-beating system of 12.8K beats per min, which will beat any bad substances in the mattress or sofa, such as dust and mites, to the surface through high-frequency beating, and then quickly suck them away. Medical-grade UV-C, ultrasonic waves and 65℃ heating system specifically designed for mites can completely kill mite eggs.
-[Pro-grade Air Purification With 6-Stage HEPA Filter and Negative Ions] RANVOO mattress vacuum is equipped with HEPA filter to achieve efficient filtration of millimeter-level particles, completely filtering out all inhaled dust, mites and allergens. RANVOO's exclusive negative oxygen ion air filtration system, which can promptly purify any dust and mites emitted from the mattress or sofa into the air when using a vacuum cleaner.
-[Easy to Use Even for Vacuum Beginners] RANVOO mattress cleaner does not require installation or any adjustments. You can start using it right after unpacking. The 400 ml large dust cup is enough to hold the dust generated by several full-house fabric cleanings, so there is no need to replace it frequently. Cleaning the dust cup and reinstalling it can also be done in tens of seconds. You can use it quickly and clean the whole house thoroughly without any tedious operations.
-[AI Chip Makes It the Best for All Fabrics] RANVOO bed vacuum is equipped with the most advanced AI chip, which can intelligently identify and adapt to any household fabrics such as mattresses, sofas, carpets and pillows, and automatically match the most suitable suction and amplitude to achieve the effect of completely removing mites and protecting the fabric itself on fabrics of different materials and depths.</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1</t>
-        </is>
-      </c>
-      <c r="K15" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>B0FX2VM7HM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Vacuums:Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O15" s="15">
-        <v>313519</v>
-      </c>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="16">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17" t="inlineStr">
-        <is>
-          <t>Futon Vacuums</t>
-        </is>
-      </c>
-      <c r="S15" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T15" s="15"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="15"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="15"/>
-      <c r="Y15" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="20"/>
-      <c r="AA15" s="4"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="19">
-        <v>30</v>
-      </c>
-      <c r="AE15" s="15"/>
-      <c r="AF15" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG15" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="20"/>
-      <c r="AI15" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ15"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="19"/>
-      <c r="AM15" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN15" s="13"/>
-      <c r="AO15" s="13"/>
-      <c r="AP15" s="20"/>
-      <c r="AQ15" s="19"/>
-      <c r="AR15" s="19"/>
-      <c r="AS15" s="14"/>
-      <c r="AT15" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="14"/>
-      <c r="AW15" s="13"/>
-      <c r="AX15" s="13"/>
-      <c r="AY15" s="13"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
-      <c r="BB15" s="13"/>
-      <c r="BC15" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD15" s="13"/>
-      <c r="BE15" s="13"/>
-      <c r="BF15" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG15" s="13"/>
-      <c r="BH15" s="14"/>
-      <c r="BI15" s="23"/>
-      <c r="BJ15" s="23"/>
-      <c r="BK15" s="23"/>
-      <c r="BL15" s="23" t="inlineStr">
-        <is>
-          <t>28.9L x 33.8W x 18.8H centimetres</t>
-        </is>
-      </c>
-      <c r="BM15" s="23"/>
-      <c r="BN15" s="23"/>
-      <c r="BO15" s="23"/>
-      <c r="BP15" s="23"/>
-      <c r="BQ15" s="23"/>
-      <c r="BR15" s="13"/>
+      <c r="BN14" s="23"/>
+      <c r="BO14" s="23"/>
+      <c r="BP14" s="23"/>
+      <c r="BQ14" s="23"/>
+      <c r="BR14" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5926,72 +5758,65 @@
     <hyperlink ref="L7" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0DBRWGZVR"/>
     <hyperlink ref="M7" r:id="rId44" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N7" r:id="rId45"/>
-    <hyperlink ref="C8" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91"/>
-    <hyperlink ref="G8" r:id="rId47" tooltip="https://www.amazon.co.uk/stores/Convenienceforyourhome/page/818AA347-F8E9-4151-B8B2-A1E50E5C29AE?lp_asin=B0D5WTVR91&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J8" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0D5WTVR91?psc=1"/>
-    <hyperlink ref="K8" r:id="rId49" tooltip="https://m.media-amazon.com/images/I/31W1ZXCx81L._AC_US200_.jpg"/>
-    <hyperlink ref="L8" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0D5WTH79H"/>
+    <hyperlink ref="C8" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
+    <hyperlink ref="G8" r:id="rId47" tooltip="https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J8" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
+    <hyperlink ref="K8" r:id="rId49" tooltip="https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg"/>
+    <hyperlink ref="L8" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B0H8S6713Z"/>
     <hyperlink ref="M8" r:id="rId51" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N8" r:id="rId52"/>
-    <hyperlink ref="C9" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W"/>
-    <hyperlink ref="G9" r:id="rId54" tooltip="https://www.amazon.co.uk/stores/Minthouz/page/10C1A6E0-EA82-42DE-BB39-8D8D80A76300?lp_asin=B0D7HF8S2W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J9" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0D7HF8S2W?psc=1"/>
-    <hyperlink ref="K9" r:id="rId56" tooltip="https://m.media-amazon.com/images/I/31O99tSwr1L._AC_US200_.jpg"/>
-    <hyperlink ref="L9" r:id="rId57" tooltip="https://www.amazon.co.uk/dp/B0H8S6713Z"/>
+    <hyperlink ref="C9" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="G9" r:id="rId54" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J9" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
+    <hyperlink ref="K9" r:id="rId56" tooltip="https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg"/>
+    <hyperlink ref="L9" r:id="rId57" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
     <hyperlink ref="M9" r:id="rId58" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N9" r:id="rId59"/>
-    <hyperlink ref="C10" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
-    <hyperlink ref="G10" r:id="rId61" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DSCSR4MB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J10" r:id="rId62" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB?psc=1"/>
-    <hyperlink ref="K10" r:id="rId63" tooltip="https://m.media-amazon.com/images/I/418QfGErb0L._AC_US200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId64" tooltip="https://www.amazon.co.uk/dp/B0DSCSR4MB"/>
+    <hyperlink ref="C10" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
+    <hyperlink ref="G10" r:id="rId61" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J10" r:id="rId62" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
+    <hyperlink ref="K10" r:id="rId63" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
+    <hyperlink ref="L10" r:id="rId64" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
     <hyperlink ref="M10" r:id="rId65" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N10" r:id="rId66"/>
-    <hyperlink ref="C11" r:id="rId67" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="G11" r:id="rId68" tooltip="https://www.amazon.co.uk/stores/TJEANLifeCleanCookBette/page/D57A3099-B34A-4AE2-BEED-A573440938CE?lp_asin=B0DSFM31F7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J11" r:id="rId69" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7?psc=1"/>
-    <hyperlink ref="K11" r:id="rId70" tooltip="https://images-na.ssl-images-amazon.com/images/I/71k7WLBBcwL._AC_US600_.jpg"/>
-    <hyperlink ref="L11" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B0DSFM31F7"/>
-    <hyperlink ref="M11" r:id="rId72" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N11" r:id="rId73"/>
-    <hyperlink ref="AW11" r:id="rId74" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
-    <hyperlink ref="C12" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
-    <hyperlink ref="G12" r:id="rId76" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J12" r:id="rId77" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
-    <hyperlink ref="K12" r:id="rId78" tooltip="https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="AW10" r:id="rId67" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A21G0QWAFKJ6UP"/>
+    <hyperlink ref="C11" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="G11" r:id="rId69" tooltip="https://www.amazon.co.uk/stores/HAUSHOF/page/127A78F6-40A3-43F5-9B80-D084EFBE3029?lp_asin=B0DTS8VCFB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J11" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB?psc=1"/>
+    <hyperlink ref="K11" r:id="rId71" tooltip="https://m.media-amazon.com/images/I/41r3fkBQX2L._AC_US200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId72" tooltip="https://www.amazon.co.uk/dp/B0DTS8VCFB"/>
+    <hyperlink ref="M11" r:id="rId73" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N11" r:id="rId74"/>
+    <hyperlink ref="C12" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
+    <hyperlink ref="G12" r:id="rId76" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk"/>
+    <hyperlink ref="J12" r:id="rId77" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
+    <hyperlink ref="K12" r:id="rId78" tooltip="https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId79" tooltip="https://www.amazon.co.uk/dp/B0FFZWJTL1"/>
     <hyperlink ref="M12" r:id="rId80" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N12" r:id="rId81"/>
-    <hyperlink ref="C13" r:id="rId82" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK"/>
-    <hyperlink ref="G13" r:id="rId83" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gxzsk"/>
-    <hyperlink ref="J13" r:id="rId84" tooltip="https://www.amazon.co.uk/dp/B0F1XRXLVK?psc=1"/>
-    <hyperlink ref="K13" r:id="rId85" tooltip="https://m.media-amazon.com/images/I/51vT9VPsfxL._AC_US200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0FFZWJTL1"/>
+    <hyperlink ref="C13" r:id="rId82" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
+    <hyperlink ref="G13" r:id="rId83" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J13" r:id="rId84" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
+    <hyperlink ref="K13" r:id="rId85" tooltip="https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg"/>
+    <hyperlink ref="L13" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
     <hyperlink ref="M13" r:id="rId87" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
     <hyperlink ref="N13" r:id="rId88"/>
-    <hyperlink ref="C14" r:id="rId89" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="G14" r:id="rId90" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FPQMRBYZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J14" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ?psc=1"/>
-    <hyperlink ref="K14" r:id="rId92" tooltip="https://images-na.ssl-images-amazon.com/images/I/81MMJHIRoeL._AC_US600_.jpg"/>
-    <hyperlink ref="L14" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0FPQMRBYZ"/>
-    <hyperlink ref="M14" r:id="rId94" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N14" r:id="rId95"/>
-    <hyperlink ref="AW14" r:id="rId96" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB"/>
-    <hyperlink ref="C15" r:id="rId97" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
-    <hyperlink ref="G15" r:id="rId98" tooltip="https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J15" r:id="rId99" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
-    <hyperlink ref="K15" r:id="rId100" tooltip="https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0FX2VM7HM"/>
-    <hyperlink ref="M15" r:id="rId102" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
-    <hyperlink ref="N15" r:id="rId103"/>
+    <hyperlink ref="AW13" r:id="rId89" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A36NXA8Q9KKCPB"/>
+    <hyperlink ref="C14" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW"/>
+    <hyperlink ref="G14" r:id="rId91" tooltip="https://www.amazon.co.uk/stores/RANVOO/page/4598C590-4586-4B0D-914B-C8811A359BA2?lp_asin=B0GJDH8XTW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J14" r:id="rId92" tooltip="https://www.amazon.co.uk/dp/B0GJDH8XTW?psc=1"/>
+    <hyperlink ref="K14" r:id="rId93" tooltip="https://m.media-amazon.com/images/I/41-S5G-ONwL._AC_US200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId94" tooltip="https://www.amazon.co.uk/dp/B0FX2VM7HM"/>
+    <hyperlink ref="M14" r:id="rId95" tooltip="https://www.amazon.co.uk/b?node=13528633031"/>
+    <hyperlink ref="N14" r:id="rId96"/>
   </hyperlinks>
-  <drawing r:id="rId104"/>
+  <drawing r:id="rId97"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -6238,7 +6063,7 @@
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>OSALADI</t>
+          <t>RANVOO</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -6257,7 +6082,7 @@
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>RANVOO</t>
+          <t>Tjean</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -6270,25 +6095,6 @@
       <c r="E13" s="15"/>
       <c r="F13" s="20"/>
       <c r="G13" s="22">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Tjean</t>
-        </is>
-      </c>
-      <c r="B14" s="15">
-        <v>0</v>
-      </c>
-      <c r="C14" s="15">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="22">
         <v>0.0</v>
       </c>
     </row>
